--- a/resources/excel_tables/skill.xlsx
+++ b/resources/excel_tables/skill.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="122211" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -22,6 +23,7 @@
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,9 +50,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -123,7 +125,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -133,44 +135,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -197,15 +199,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -232,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -244,131 +244,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -384,138 +413,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>SkillID</t>
+          <t>skill_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>class_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ManaCost</t>
+          <t>type</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cooldown</t>
+          <t>target_type</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>range</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>cooldown</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>AreaRadius</t>
+          <t>mp_cost</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>cast_time</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Effects</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>DamageType</t>
+          <t>element_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>EffectType</t>
+          <t>description</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>CooldownGrowth</t>
+          <t>effect</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>DamageGrowth</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>RangeGrowth</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>RequiredLevel</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>AnimationID</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>SoundID</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>IconID</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>PreSkillID</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>BuffID</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>SkillCastTime</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>SkillProjectileSpeed</t>
+          <t>required_level</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>劈砍</t>
+          <t>火球术</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -524,112 +513,1525 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>10</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>20</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>基础的物理攻击</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>[{"type":1,"value":20}]</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>释放一个火球攻击单个目标</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>造成火焰伤害</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>fire_ball.png</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1002</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>火球术</t>
+          <t>冰箭术</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
         <v>15</v>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>60</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ice</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>释放一支冰箭攻击单个目标，有几率减速</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>造成冰霜伤害，50%几率减速目标</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ice_arrow.png</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>发射一个火球</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>[{"type":2,"value":30}]</t>
-        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>闪电链</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>lightning</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>释放闪电链攻击多个目标</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>造成雷电伤害，可连锁3个目标</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>lightning_chain.png</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>魔法护盾</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>arcane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>创建魔法护盾吸收伤害</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>吸收100点伤害，持续10秒</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>magic_shield.png</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>火球雨</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>80</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>召唤火球雨攻击区域内的所有目标</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>造成火焰伤害，覆盖10x10范围</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>fire_rain.png</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>魔法精通</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>arcane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>提高魔法伤害</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>魔法伤害提高10%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>magic_mastery.png</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>猛击</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>45</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>对目标造成猛烈攻击</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>造成物理伤害</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>bash.png</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>嘲讽</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>嘲讽目标，使其攻击自己</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>强制目标攻击自己，持续5秒</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>taunt.png</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>旋风斩</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>治疗术</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>35</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>旋转攻击周围多个目标</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>攻击周围3个目标</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>whirlwind.png</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>盾牌格挡</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>使用盾牌格挡伤害</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>减少50%伤害，持续3秒</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>shield_block.png</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>冲锋</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>60</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>冲锋到目标身边并造成伤害</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>冲锋到目标身边，造成伤害并眩晕1秒</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>charge.png</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>武器精通</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>提高武器伤害</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>物理伤害提高10%</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>weapon_mastery.png</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3001</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>普通射击</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>使用弓箭攻击单个目标</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>造成物理伤害</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>normal_shot.png</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3002</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>瞄准射击</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>20</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>70</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>精确瞄准并射击目标</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>造成高额物理伤害，有20%几率暴击</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>aim_shot.png</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3003</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>多重箭</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>25</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>30</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>同时射出多支箭攻击多个目标</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>攻击3个目标</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>multi_shot.png</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3004</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>陷阱</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>恢复生命值</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>[{"type":3,"value":50}]</t>
-        </is>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>50</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>放置陷阱，敌人踩中后触发</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>对踩中陷阱的敌人造成伤害并减速</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>trap.png</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3005</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>鹰击长空</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>25</v>
+      </c>
+      <c r="H18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" t="n">
+        <v>35</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>80</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>召唤鹰群攻击区域内的所有目标</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>造成物理伤害，覆盖15x15范围</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>eagle_strike.png</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3006</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>精准射击</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>提高弓箭命中率和暴击率</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>命中率提高5%，暴击率提高3%</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>precision_shot.png</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4001</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>背刺</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>55</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>从背后攻击目标</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>造成物理伤害，背后攻击伤害提高50%</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>back_stab.png</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4002</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>隐身</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" t="n">
+        <v>30</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>进入隐身状态</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>隐身10秒，攻击或被攻击后现身</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>stealth.png</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4003</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>毒刃</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>45</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>用毒刃攻击目标</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>造成物理伤害并附加中毒效果，持续5秒</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>poison_blade.png</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4004</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>闪避</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>15</v>
+      </c>
+      <c r="I23" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>提高闪避率</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>闪避率提高50%，持续5秒</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>evasion.png</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4005</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致命一击</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" t="n">
+        <v>25</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>100</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>对目标造成致命伤害</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>造成高额物理伤害，有30%几率暴击</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>critical_strike.png</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4006</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>暗杀精通</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>提高暴击率和暴击伤害</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>暴击率提高5%，暴击伤害提高20%</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>assassination_mastery.png</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
